--- a/data/trans_orig/IP07A01-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP07A01-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse bien y en forma en 2007 (tasa de respuesta: 99,7%)</t>
+          <t>Menores según la frecuencia de sentirse bien y en forma, percibida por el adulto en 2007 (tasa de respuesta: 99,7%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22540</t>
+          <t>22300</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33739</t>
+          <t>33701</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>66,58%</t>
+          <t>66,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17984</t>
+          <t>18111</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29344</t>
+          <t>29064</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>38,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>62,13%</t>
+          <t>61,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>43933</t>
+          <t>43466</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>59966</t>
+          <t>59618</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>44,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>61,25%</t>
+          <t>60,89%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10259</t>
+          <t>10262</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21121</t>
+          <t>20364</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,68%</t>
+          <t>40,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15225</t>
+          <t>15207</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26257</t>
+          <t>26546</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>56,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>28925</t>
+          <t>29013</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>44159</t>
+          <t>44359</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,1%</t>
+          <t>45,31%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2774</t>
+          <t>2871</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10907</t>
+          <t>10779</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4074</t>
+          <t>4583</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3749</t>
+          <t>3992</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11856</t>
+          <t>12526</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,79%</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3897</t>
+          <t>4334</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4013</t>
+          <t>3320</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>426</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5763</t>
+          <t>5834</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,96%</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3322</t>
+          <t>3344</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3364</t>
+          <t>3359</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>94354</t>
+          <t>94983</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>117533</t>
+          <t>117840</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>46,23%</t>
+          <t>46,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>57,58%</t>
+          <t>57,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>112494</t>
+          <t>111017</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>136782</t>
+          <t>136536</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>47,27%</t>
+          <t>46,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,48%</t>
+          <t>57,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>213837</t>
+          <t>213145</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>246774</t>
+          <t>247939</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,37%</t>
+          <t>48,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,82%</t>
+          <t>56,08%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>73169</t>
+          <t>72410</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>96255</t>
+          <t>94407</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>35,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>47,16%</t>
+          <t>46,25%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>85119</t>
+          <t>85676</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>109115</t>
+          <t>109123</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>36,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>45,85%</t>
+          <t>45,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>164072</t>
+          <t>163176</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>197243</t>
+          <t>198112</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>44,81%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7186</t>
+          <t>7119</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18411</t>
+          <t>18245</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6536</t>
+          <t>6630</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17274</t>
+          <t>17176</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>15722</t>
+          <t>16380</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>31328</t>
+          <t>31457</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,12%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>684</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>6475</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2085</t>
+          <t>2416</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9212</t>
+          <t>9720</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4328</t>
+          <t>3993</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13051</t>
+          <t>12754</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -1907,7 +1907,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2969</t>
+          <t>3268</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3301</t>
+          <t>2982</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,67%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19852</t>
+          <t>20478</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>33315</t>
+          <t>33684</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>50,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>23160</t>
+          <t>22589</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>35364</t>
+          <t>35913</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>37,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>58,56%</t>
+          <t>59,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>45865</t>
+          <t>47023</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>64710</t>
+          <t>64631</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>36,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>50,85%</t>
+          <t>50,79%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28612</t>
+          <t>28218</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>42229</t>
+          <t>41581</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>63,17%</t>
+          <t>62,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>22360</t>
+          <t>22063</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>35098</t>
+          <t>34666</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>36,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>58,11%</t>
+          <t>57,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>54097</t>
+          <t>55006</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>73319</t>
+          <t>72919</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>43,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>57,62%</t>
+          <t>57,3%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>677</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5525</t>
+          <t>5743</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>664</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6637</t>
+          <t>6024</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2133</t>
+          <t>2064</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>9702</t>
+          <t>9266</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,28%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>523</t>
+          <t>514</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5313</t>
+          <t>5030</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>524</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4821</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3979</t>
+          <t>4386</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3959</t>
+          <t>4546</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>146270</t>
+          <t>146117</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>175392</t>
+          <t>175764</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>45,48%</t>
+          <t>45,43%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>54,53%</t>
+          <t>54,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>161972</t>
+          <t>162715</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>191829</t>
+          <t>193038</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>46,87%</t>
+          <t>47,08%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>55,51%</t>
+          <t>55,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>317820</t>
+          <t>318110</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>358970</t>
+          <t>359192</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>47,63%</t>
+          <t>47,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>53,83%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>119226</t>
+          <t>119865</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>149360</t>
+          <t>149069</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>46,44%</t>
+          <t>46,35%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>131640</t>
+          <t>131119</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>161865</t>
+          <t>160967</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>37,94%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>46,58%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>262176</t>
+          <t>259218</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>302540</t>
+          <t>299347</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>44,86%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>13418</t>
+          <t>14449</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>28933</t>
+          <t>28140</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>10434</t>
+          <t>9348</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>22547</t>
+          <t>22386</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>25584</t>
+          <t>26008</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>44224</t>
+          <t>44577</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,68%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2646</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>10764</t>
+          <t>10428</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2703</t>
+          <t>2614</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10454</t>
+          <t>10085</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6971</t>
+          <t>7370</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>17868</t>
+          <t>18371</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3960</t>
+          <t>4470</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4915</t>
+          <t>3820</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>593</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5363</t>
+          <t>6148</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse bien y en forma en 2012 (tasa de respuesta: 98,12%)</t>
+          <t>Menores según la frecuencia de sentirse bien y en forma, percibida por el adulto en 2012 (tasa de respuesta: 98,12%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11392</t>
+          <t>10972</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22529</t>
+          <t>22953</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>43,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10270</t>
+          <t>10199</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20995</t>
+          <t>20476</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,79%</t>
+          <t>44,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24492</t>
+          <t>24301</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39667</t>
+          <t>39281</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>39,7%</t>
         </is>
       </c>
     </row>
@@ -3805,12 +3805,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26241</t>
+          <t>26065</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>38211</t>
+          <t>37933</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3820,12 +3820,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>49,43%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>71,98%</t>
+          <t>71,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20429</t>
+          <t>20262</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31610</t>
+          <t>31470</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>44,55%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>68,94%</t>
+          <t>68,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>49938</t>
+          <t>50291</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>66355</t>
+          <t>67706</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>50,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>68,44%</t>
         </is>
       </c>
     </row>
@@ -3918,12 +3918,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1369</t>
+          <t>1408</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7837</t>
+          <t>7559</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1348</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9397</t>
+          <t>9228</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4095</t>
+          <t>3977</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14312</t>
+          <t>13336</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4003,12 +4003,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>13,48%</t>
         </is>
       </c>
     </row>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2961</t>
+          <t>2674</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3117</t>
+          <t>3721</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5004</t>
+          <t>4528</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4121,7 +4121,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,58%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>61343</t>
+          <t>60890</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>83389</t>
+          <t>83251</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>40,45%</t>
+          <t>40,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>89507</t>
+          <t>90815</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>114273</t>
+          <t>115344</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,13%</t>
+          <t>39,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>50,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>157020</t>
+          <t>158779</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>193163</t>
+          <t>193900</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>36,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,42%</t>
+          <t>44,59%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>109438</t>
+          <t>109770</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>132148</t>
+          <t>133369</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>53,09%</t>
+          <t>53,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>64,1%</t>
+          <t>64,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>97343</t>
+          <t>95971</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>122026</t>
+          <t>120916</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>41,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>53,35%</t>
+          <t>52,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>212059</t>
+          <t>212219</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>247681</t>
+          <t>246339</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>48,76%</t>
+          <t>48,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>56,96%</t>
+          <t>56,65%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5915</t>
+          <t>5677</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16437</t>
+          <t>15346</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5587</t>
+          <t>5777</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15574</t>
+          <t>16051</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>13251</t>
+          <t>13126</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>27338</t>
+          <t>27300</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,28%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>749</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7602</t>
+          <t>7126</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2157</t>
+          <t>2153</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9633</t>
+          <t>9763</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4315</t>
+          <t>4709</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13977</t>
+          <t>14321</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>658</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6181</t>
+          <t>6868</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>634</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6747</t>
+          <t>6304</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15986</t>
+          <t>16058</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28994</t>
+          <t>29396</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>45,72%</t>
+          <t>46,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11389</t>
+          <t>11427</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22475</t>
+          <t>22402</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,25%</t>
+          <t>39,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>32007</t>
+          <t>30449</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>48761</t>
+          <t>48026</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>39,79%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>26899</t>
+          <t>27293</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>40298</t>
+          <t>41036</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>43,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>63,54%</t>
+          <t>64,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>28689</t>
+          <t>28838</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>40928</t>
+          <t>40823</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>50,1%</t>
+          <t>50,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>71,47%</t>
+          <t>71,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>60160</t>
+          <t>60423</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>77775</t>
+          <t>78447</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>49,85%</t>
+          <t>50,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>64,45%</t>
+          <t>65,0%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2717</t>
+          <t>2903</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10242</t>
+          <t>11343</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1968</t>
+          <t>1453</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9292</t>
+          <t>9296</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5332,7 +5332,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6143</t>
+          <t>6652</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>16563</t>
+          <t>16596</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,75%</t>
         </is>
       </c>
     </row>
@@ -5400,7 +5400,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3866</t>
+          <t>3590</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5435,7 +5435,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5170</t>
+          <t>5733</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5470,7 +5470,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,29%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>97688</t>
+          <t>96566</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>125616</t>
+          <t>125639</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>38,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>120006</t>
+          <t>119569</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>148540</t>
+          <t>148468</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>44,76%</t>
+          <t>44,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>226121</t>
+          <t>225150</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>265388</t>
+          <t>267728</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>40,91%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>173214</t>
+          <t>172786</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>201300</t>
+          <t>202834</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>53,69%</t>
+          <t>53,55%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>62,39%</t>
+          <t>62,87%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>155182</t>
+          <t>153086</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>184438</t>
+          <t>184335</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>46,76%</t>
+          <t>46,13%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>55,58%</t>
+          <t>55,55%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>337710</t>
+          <t>335471</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>378456</t>
+          <t>379046</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>51,6%</t>
+          <t>51,26%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>57,83%</t>
+          <t>57,92%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>13435</t>
+          <t>13508</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>27228</t>
+          <t>27030</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>12975</t>
+          <t>12544</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>27761</t>
+          <t>26910</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>29337</t>
+          <t>29242</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>49892</t>
+          <t>48475</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,41%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1458</t>
+          <t>1516</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8956</t>
+          <t>8874</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3219</t>
+          <t>3457</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>12334</t>
+          <t>12462</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6238</t>
+          <t>6535</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>18249</t>
+          <t>16992</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -6225,47 +6225,47 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
+          <t>629</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>6458</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>1,95%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>2559</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
           <t>633</t>
         </is>
       </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>5944</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>1,79%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>2559</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>633</t>
-        </is>
-      </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5890</t>
+          <t>6455</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6280,7 +6280,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -6456,7 +6456,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse bien y en forma en 2016 (tasa de respuesta: 99,02%)</t>
+          <t>Menores según la frecuencia de sentirse bien y en forma, percibida por el adulto en 2016 (tasa de respuesta: 99,02%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6651,12 +6651,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10866</t>
+          <t>12010</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20419</t>
+          <t>21159</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6666,12 +6666,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>37,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>64,18%</t>
+          <t>66,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6686,12 +6686,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15746</t>
+          <t>16070</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25639</t>
+          <t>26055</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>43,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>71,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6721,12 +6721,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30009</t>
+          <t>30869</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44330</t>
+          <t>44427</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>43,84%</t>
+          <t>45,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>64,76%</t>
+          <t>64,9%</t>
         </is>
       </c>
     </row>
@@ -6764,12 +6764,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8746</t>
+          <t>8225</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17609</t>
+          <t>17361</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6779,12 +6779,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>55,35%</t>
+          <t>54,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9611</t>
+          <t>8827</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19416</t>
+          <t>18800</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,99%</t>
+          <t>51,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20892</t>
+          <t>20112</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>33591</t>
+          <t>33386</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>49,07%</t>
+          <t>48,77%</t>
         </is>
       </c>
     </row>
@@ -6877,12 +6877,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>557</t>
+          <t>551</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5705</t>
+          <t>6001</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6892,12 +6892,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3977</t>
+          <t>4085</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6932,7 +6932,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>897</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6838</t>
+          <t>6905</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,09%</t>
         </is>
       </c>
     </row>
@@ -6995,7 +6995,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3311</t>
+          <t>3149</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7030,7 +7030,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4937</t>
+          <t>4867</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7045,7 +7045,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7065,7 +7065,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5197</t>
+          <t>5361</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7080,7 +7080,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,83%</t>
         </is>
       </c>
     </row>
@@ -7333,12 +7333,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>117915</t>
+          <t>115865</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>143135</t>
+          <t>143121</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7348,12 +7348,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>47,06%</t>
+          <t>46,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>57,13%</t>
+          <t>57,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>127293</t>
+          <t>128709</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>153868</t>
+          <t>154656</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7383,12 +7383,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>51,61%</t>
+          <t>52,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,38%</t>
+          <t>62,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>253617</t>
+          <t>253857</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>289588</t>
+          <t>290859</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7418,12 +7418,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>51,01%</t>
+          <t>51,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,24%</t>
+          <t>58,5%</t>
         </is>
       </c>
     </row>
@@ -7446,12 +7446,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>91185</t>
+          <t>91420</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>116398</t>
+          <t>116971</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,46%</t>
+          <t>46,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>78720</t>
+          <t>78852</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>105215</t>
+          <t>104652</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7496,12 +7496,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>42,66%</t>
+          <t>42,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>176964</t>
+          <t>175070</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>212787</t>
+          <t>211690</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7531,12 +7531,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>42,57%</t>
         </is>
       </c>
     </row>
@@ -7559,12 +7559,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6406</t>
+          <t>6837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18863</t>
+          <t>18442</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6089</t>
+          <t>6066</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17418</t>
+          <t>17117</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>15188</t>
+          <t>14801</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>32058</t>
+          <t>31415</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,32%</t>
         </is>
       </c>
     </row>
@@ -7672,12 +7672,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>837</t>
+          <t>725</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7428</t>
+          <t>7570</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7687,12 +7687,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7712,7 +7712,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8224</t>
+          <t>7341</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7742,12 +7742,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2796</t>
+          <t>2798</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11809</t>
+          <t>11527</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7762,7 +7762,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7785,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>618</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7230</t>
+          <t>6801</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7800,12 +7800,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7825,7 +7825,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3289</t>
+          <t>3480</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7840,7 +7840,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1026</t>
+          <t>697</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7419</t>
+          <t>7577</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -8015,12 +8015,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>28250</t>
+          <t>28022</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>43203</t>
+          <t>42497</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8030,12 +8030,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>37,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>58,07%</t>
+          <t>57,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>41061</t>
+          <t>41587</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>55532</t>
+          <t>56014</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8065,12 +8065,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>52,6%</t>
+          <t>53,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>71,14%</t>
+          <t>71,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>73198</t>
+          <t>74797</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>95119</t>
+          <t>95990</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>49,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>62,39%</t>
+          <t>62,96%</t>
         </is>
       </c>
     </row>
@@ -8128,12 +8128,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>25648</t>
+          <t>25643</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>40699</t>
+          <t>40416</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8148,7 +8148,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>54,7%</t>
+          <t>54,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16325</t>
+          <t>16625</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>30162</t>
+          <t>29950</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8178,12 +8178,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8198,12 +8198,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>45942</t>
+          <t>45846</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>66964</t>
+          <t>66187</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>43,92%</t>
+          <t>43,41%</t>
         </is>
       </c>
     </row>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>701</t>
+          <t>726</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6506</t>
+          <t>6429</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8276,12 +8276,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1966</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8817</t>
+          <t>8982</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8291,12 +8291,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8311,12 +8311,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4011</t>
+          <t>4036</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>13412</t>
+          <t>12305</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8326,12 +8326,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,07%</t>
         </is>
       </c>
     </row>
@@ -8354,12 +8354,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>625</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6110</t>
+          <t>5853</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8369,12 +8369,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8394,7 +8394,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6329</t>
+          <t>5693</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8409,7 +8409,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8424,12 +8424,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1082</t>
+          <t>1415</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8544</t>
+          <t>8586</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8439,12 +8439,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,63%</t>
         </is>
       </c>
     </row>
@@ -8472,7 +8472,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4002</t>
+          <t>5104</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8487,7 +8487,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8542,7 +8542,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4743</t>
+          <t>5915</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8557,7 +8557,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -8697,12 +8697,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>167663</t>
+          <t>167168</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>197762</t>
+          <t>196516</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8712,12 +8712,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>46,99%</t>
+          <t>46,86%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>55,43%</t>
+          <t>55,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8732,12 +8732,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>196248</t>
+          <t>195992</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>226769</t>
+          <t>227053</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8747,12 +8747,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>54,31%</t>
+          <t>54,24%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>62,75%</t>
+          <t>62,83%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8767,12 +8767,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>373805</t>
+          <t>373283</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>416407</t>
+          <t>415747</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8782,12 +8782,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>52,05%</t>
+          <t>51,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>57,98%</t>
+          <t>57,89%</t>
         </is>
       </c>
     </row>
@@ -8810,12 +8810,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>134047</t>
+          <t>134553</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>165301</t>
+          <t>164623</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8825,12 +8825,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>37,57%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>46,14%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8845,12 +8845,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>112117</t>
+          <t>111323</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>142802</t>
+          <t>142856</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8860,12 +8860,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>39,53%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8880,12 +8880,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>253596</t>
+          <t>254053</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>297037</t>
+          <t>298391</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8895,12 +8895,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>41,55%</t>
         </is>
       </c>
     </row>
@@ -8923,12 +8923,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>10591</t>
+          <t>10479</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>24344</t>
+          <t>24389</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8938,12 +8938,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8958,12 +8958,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>10484</t>
+          <t>10284</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>23205</t>
+          <t>23817</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8973,12 +8973,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8993,12 +8993,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>22730</t>
+          <t>23229</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>42094</t>
+          <t>42038</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9008,12 +9008,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,85%</t>
         </is>
       </c>
     </row>
@@ -9036,12 +9036,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2567</t>
+          <t>2236</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>10719</t>
+          <t>10961</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2475</t>
+          <t>2286</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>12137</t>
+          <t>11336</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9086,12 +9086,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6762</t>
+          <t>6948</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>19621</t>
+          <t>19107</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9121,12 +9121,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -9149,12 +9149,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>791</t>
+          <t>789</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>7547</t>
+          <t>7802</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9169,7 +9169,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9189,7 +9189,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3939</t>
+          <t>4375</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9204,7 +9204,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1249</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>8418</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -9415,7 +9415,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse bien y en forma en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según la frecuencia de sentirse bien y en forma, percibida por el adulto en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9610,12 +9610,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17330</t>
+          <t>17519</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25360</t>
+          <t>25525</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9625,12 +9625,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>60,63%</t>
+          <t>61,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>89,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9645,12 +9645,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5036</t>
+          <t>5084</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14283</t>
+          <t>14098</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9660,12 +9660,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>51,87%</t>
+          <t>51,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9680,12 +9680,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22776</t>
+          <t>24657</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38686</t>
+          <t>39494</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9695,12 +9695,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>40,59%</t>
+          <t>43,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>68,94%</t>
+          <t>70,38%</t>
         </is>
       </c>
     </row>
@@ -9723,12 +9723,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2508</t>
+          <t>2548</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10312</t>
+          <t>10333</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9738,12 +9738,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>36,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9758,12 +9758,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6708</t>
+          <t>6816</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16422</t>
+          <t>16995</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9773,12 +9773,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>59,64%</t>
+          <t>61,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9793,12 +9793,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10682</t>
+          <t>10781</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>24566</t>
+          <t>24418</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9808,12 +9808,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>43,78%</t>
+          <t>43,51%</t>
         </is>
       </c>
     </row>
@@ -9841,7 +9841,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2038</t>
+          <t>2469</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9856,7 +9856,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9871,12 +9871,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1039</t>
+          <t>1257</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9579</t>
+          <t>9190</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9886,12 +9886,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9906,12 +9906,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1447</t>
+          <t>1470</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10359</t>
+          <t>9973</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9921,12 +9921,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>17,77%</t>
         </is>
       </c>
     </row>
@@ -9984,12 +9984,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>849</t>
+          <t>829</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7699</t>
+          <t>7104</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9999,12 +9999,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10019,12 +10019,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>840</t>
+          <t>828</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7183</t>
+          <t>7905</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>14,09%</t>
         </is>
       </c>
     </row>
@@ -10067,7 +10067,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3273</t>
+          <t>2519</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10082,7 +10082,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10137,7 +10137,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2939</t>
+          <t>3334</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10152,7 +10152,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,94%</t>
         </is>
       </c>
     </row>
@@ -10292,12 +10292,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>154930</t>
+          <t>155220</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>202089</t>
+          <t>203037</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10307,12 +10307,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>59,31%</t>
+          <t>59,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>77,36%</t>
+          <t>77,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10327,12 +10327,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>179641</t>
+          <t>180289</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>218152</t>
+          <t>221306</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10342,12 +10342,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>58,09%</t>
+          <t>58,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>70,54%</t>
+          <t>71,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10362,12 +10362,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>344278</t>
+          <t>347122</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>404218</t>
+          <t>402763</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10377,12 +10377,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>60,35%</t>
+          <t>60,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>70,86%</t>
+          <t>70,6%</t>
         </is>
       </c>
     </row>
@@ -10405,12 +10405,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>54185</t>
+          <t>52708</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>95569</t>
+          <t>93752</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10420,12 +10420,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10440,12 +10440,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>68593</t>
+          <t>67720</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>103257</t>
+          <t>101981</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10455,12 +10455,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10475,12 +10475,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>137666</t>
+          <t>134527</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>190320</t>
+          <t>187170</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10490,12 +10490,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>32,81%</t>
         </is>
       </c>
     </row>
@@ -10518,12 +10518,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2338</t>
+          <t>2458</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11229</t>
+          <t>10752</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10533,12 +10533,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10553,12 +10553,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10676</t>
+          <t>11094</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>39249</t>
+          <t>38089</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10568,12 +10568,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10588,12 +10588,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>15339</t>
+          <t>15233</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>44475</t>
+          <t>45716</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10603,12 +10603,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>8,01%</t>
         </is>
       </c>
     </row>
@@ -10631,12 +10631,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1540</t>
+          <t>1533</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10906</t>
+          <t>10583</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10651,7 +10651,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10666,12 +10666,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1435</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7313</t>
+          <t>7510</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10681,12 +10681,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10701,12 +10701,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4234</t>
+          <t>4044</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14242</t>
+          <t>14546</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10716,12 +10716,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -10749,7 +10749,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4533</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10764,7 +10764,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10784,7 +10784,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6089</t>
+          <t>5165</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10799,7 +10799,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10819,7 +10819,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6417</t>
+          <t>6889</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10834,7 +10834,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -10974,12 +10974,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>32799</t>
+          <t>32302</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>47566</t>
+          <t>47880</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>39,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>58,88%</t>
+          <t>59,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>60004</t>
+          <t>59595</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>77835</t>
+          <t>78100</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>58,29%</t>
+          <t>57,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>75,61%</t>
+          <t>75,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>97528</t>
+          <t>96658</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>121403</t>
+          <t>120914</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>53,08%</t>
+          <t>52,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>66,08%</t>
+          <t>65,81%</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28447</t>
+          <t>29105</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>43739</t>
+          <t>43300</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11102,12 +11102,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>54,15%</t>
+          <t>53,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20865</t>
+          <t>21199</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>36535</t>
+          <t>37727</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>36,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>53104</t>
+          <t>52651</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>75692</t>
+          <t>76210</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>41,48%</t>
         </is>
       </c>
     </row>
@@ -11200,12 +11200,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>623</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6874</t>
+          <t>6441</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11215,12 +11215,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1661</t>
+          <t>1204</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11972</t>
+          <t>10679</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2970</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>14219</t>
+          <t>14254</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,76%</t>
         </is>
       </c>
     </row>
@@ -11318,7 +11318,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>5808</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11388,7 +11388,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4959</t>
+          <t>4832</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11403,7 +11403,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -11431,7 +11431,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4968</t>
+          <t>3910</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11446,7 +11446,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11466,7 +11466,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4205</t>
+          <t>4688</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11481,7 +11481,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11501,7 +11501,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5981</t>
+          <t>4950</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11516,7 +11516,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>214613</t>
+          <t>213956</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>266994</t>
+          <t>264072</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>57,91%</t>
+          <t>57,73%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>72,04%</t>
+          <t>71,26%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>258431</t>
+          <t>255058</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>303439</t>
+          <t>299842</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>58,77%</t>
+          <t>58,0%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>69,01%</t>
+          <t>68,19%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>481176</t>
+          <t>484370</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>548243</t>
+          <t>550631</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>59,38%</t>
+          <t>59,77%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>67,66%</t>
+          <t>67,95%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>91522</t>
+          <t>93036</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>138487</t>
+          <t>139493</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>37,64%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>104928</t>
+          <t>106867</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>144031</t>
+          <t>144004</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11819,7 +11819,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>212721</t>
+          <t>209710</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>273963</t>
+          <t>271121</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>33,46%</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4116</t>
+          <t>4352</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>14100</t>
+          <t>13768</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>17458</t>
+          <t>17927</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>48091</t>
+          <t>46546</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>24310</t>
+          <t>25207</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>55680</t>
+          <t>57831</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,14%</t>
         </is>
       </c>
     </row>
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2290</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>12862</t>
+          <t>12070</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12010,12 +12010,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12030,12 +12030,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>12285</t>
+          <t>12532</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12045,12 +12045,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12065,12 +12065,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6787</t>
+          <t>7351</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>19769</t>
+          <t>20677</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12080,12 +12080,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -12108,12 +12108,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>527</t>
+          <t>166</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>6597</t>
+          <t>5844</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12123,12 +12123,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12148,7 +12148,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>6390</t>
+          <t>7083</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12163,7 +12163,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12178,12 +12178,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1379</t>
+          <t>1392</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>8797</t>
+          <t>9124</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12198,7 +12198,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
